--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_magallanes.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:50</t>
+    <t xml:space="preserve">2026-09-09 20:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_magallanes.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:13</t>
+    <t xml:space="preserve">2026-09-18 17:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_magallanes.xlsx
@@ -30,39 +30,39 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Natales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabo de Hornos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punta Arenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porvenir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primavera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laguna Blanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Verde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timaukel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Gregorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torres del Paine</t>
+  </si>
+  <si>
     <t xml:space="preserve">Antártica</t>
   </si>
   <si>
-    <t xml:space="preserve">Torres del Paine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Gregorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timaukel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Verde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laguna Blanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primavera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porvenir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Punta Arenas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabo de Hornos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:06</t>
+    <t xml:space="preserve">2026-09-27 21:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -492,13 +492,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>22</v>
+        <v>29253</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>148</v>
+        <v>24447</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>14.86</v>
+        <v>119.66</v>
       </c>
     </row>
     <row r="3">
@@ -506,13 +506,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>203</v>
+        <v>1996</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1069</v>
+        <v>1973</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>18.99</v>
+        <v>101.17</v>
       </c>
     </row>
     <row r="4">
@@ -520,13 +520,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>237</v>
+        <v>144201</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>658</v>
+        <v>144938</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>36.02</v>
+        <v>99.49</v>
       </c>
     </row>
     <row r="5">
@@ -534,13 +534,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>148</v>
+        <v>7487</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>278</v>
+        <v>7570</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>53.24</v>
+        <v>98.9</v>
       </c>
     </row>
     <row r="6">
@@ -548,13 +548,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>143</v>
+        <v>575</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>205</v>
+        <v>679</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>69.76</v>
+        <v>84.68</v>
       </c>
     </row>
     <row r="7">
@@ -576,13 +576,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>575</v>
+        <v>143</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>679</v>
+        <v>205</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>84.68</v>
+        <v>69.76</v>
       </c>
     </row>
     <row r="9">
@@ -590,13 +590,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>7487</v>
+        <v>148</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7570</v>
+        <v>278</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>98.9</v>
+        <v>53.24</v>
       </c>
     </row>
     <row r="10">
@@ -604,13 +604,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>144201</v>
+        <v>237</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>144938</v>
+        <v>658</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>99.49</v>
+        <v>36.02</v>
       </c>
     </row>
     <row r="11">
@@ -618,13 +618,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1996</v>
+        <v>203</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1973</v>
+        <v>1069</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>101.17</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="12">
@@ -632,13 +632,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>29253</v>
+        <v>22</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>24447</v>
+        <v>148</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>119.66</v>
+        <v>14.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_magallanes.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_magallanes.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:53</t>
+    <t xml:space="preserve">2026-10-05 05:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
